--- a/api/data/rosters/optimized_roster.xlsx
+++ b/api/data/rosters/optimized_roster.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -482,12 +482,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SURG;ED</t>
+          <t>SURG</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -532,12 +532,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -557,12 +557,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ICU;SURG</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -587,11 +587,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>SURG</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -607,16 +607,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ED;SURG</t>
+          <t>SURG</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -632,16 +632,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ICU;SURG</t>
+          <t>SURG</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -662,11 +662,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ICU</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -687,7 +687,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SURG;GEN</t>
+          <t>SURG</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -712,7 +712,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ICU;ED</t>
+          <t>ICU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -732,12 +732,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GEN;ED</t>
+          <t>ICU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -782,12 +782,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GEN;ED</t>
+          <t>ICU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ICU;SURG</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -862,11 +862,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ICU;SURG</t>
+          <t>SURG</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -882,12 +882,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ED;GEN</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -907,16 +907,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SURG;GEN</t>
+          <t>ICU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -941,207 +941,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>N021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Nurse_21</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>GEN;ICU</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>N022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Nurse_22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ICU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>N023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Nurse_23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>N024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Nurse_24</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ED</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>N025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Nurse_25</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ICU</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>N026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Nurse_26</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ICU;ED</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>N027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Nurse_27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ED</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>N028</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Nurse_28</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1155,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D225"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1183,7 +983,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1196,14 +996,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N003</t>
+          <t>N007</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1216,14 +1016,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N008</t>
+          <t>N010</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1236,14 +1036,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>N027</t>
+          <t>N008</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1256,54 +1056,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>N010</t>
+          <t>N004</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>N017</t>
+          <t>N011</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>N004</t>
+          <t>N017</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1312,18 +1112,18 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N004</t>
+          <t>N017</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1332,107 +1132,107 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>N027</t>
+          <t>N020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N012</t>
+          <t>N009</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N013</t>
+          <t>N004</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>N005</t>
+          <t>N014</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N016</t>
+          <t>N019</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1443,192 +1243,192 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>N014</t>
+          <t>N009</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>N021</t>
+          <t>N015</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>N010</t>
+          <t>N005</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>N015</t>
+          <t>N006</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>N009</t>
+          <t>N020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>N018</t>
+          <t>N010</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>N019</t>
+          <t>N003</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>N008</t>
+          <t>N012</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>N006</t>
+          <t>N007</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1636,19 +1436,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>N015</t>
+          <t>N003</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1656,19 +1456,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>N026</t>
+          <t>N018</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1676,19 +1476,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>N012</t>
+          <t>N011</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1696,14 +1496,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>N003</t>
+          <t>N010</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1712,18 +1512,18 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>N025</t>
+          <t>N017</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1732,58 +1532,58 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>N028</t>
+          <t>N007</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>N018</t>
+          <t>N007</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>N013</t>
+          <t>N001</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1792,18 +1592,18 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>N021</t>
+          <t>N004</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1812,38 +1612,38 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>N007</t>
+          <t>N002</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>N024</t>
+          <t>N009</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,18 +1652,18 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>N022</t>
+          <t>N001</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1872,18 +1672,18 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>N018</t>
+          <t>N016</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1892,18 +1692,18 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>N028</t>
+          <t>N019</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1912,38 +1712,38 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>N019</t>
+          <t>N006</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>N018</t>
+          <t>N014</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1952,18 +1752,18 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>N028</t>
+          <t>N008</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1972,18 +1772,18 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>N001</t>
+          <t>N020</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1992,83 +1792,83 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>N004</t>
+          <t>N017</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>N015</t>
+          <t>N013</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>N019</t>
+          <t>N009</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>N013</t>
+          <t>N008</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2076,19 +1876,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>N028</t>
+          <t>N015</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2096,19 +1896,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>N020</t>
+          <t>N016</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2116,19 +1916,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>N027</t>
+          <t>N005</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2136,19 +1936,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>N010</t>
+          <t>N007</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2156,19 +1956,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>N026</t>
+          <t>N016</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2176,19 +1976,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>N010</t>
+          <t>N003</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -2196,19 +1996,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>N026</t>
+          <t>N020</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2216,154 +2016,154 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>N025</t>
+          <t>N013</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>N004</t>
+          <t>N011</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>N007</t>
+          <t>N002</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>N014</t>
+          <t>N010</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>N022</t>
+          <t>N006</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>N019</t>
+          <t>N018</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>N018</t>
+          <t>N009</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N006</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2372,78 +2172,78 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>N007</t>
+          <t>N002</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>N020</t>
+          <t>N019</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>N022</t>
+          <t>N007</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>N015</t>
+          <t>N017</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2452,58 +2252,58 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>N008</t>
+          <t>N003</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>N007</t>
+          <t>N012</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>N024</t>
+          <t>N011</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2512,18 +2312,18 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>N015</t>
+          <t>N010</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2532,7 +2332,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2543,7 +2343,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2552,18 +2352,18 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>N022</t>
+          <t>N007</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2572,18 +2372,18 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>N005</t>
+          <t>N013</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2596,14 +2396,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>N027</t>
+          <t>N008</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2616,14 +2416,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>N017</t>
+          <t>N002</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2636,14 +2436,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>N022</t>
+          <t>N019</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2656,54 +2456,54 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>N005</t>
+          <t>N016</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>N017</t>
+          <t>N011</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>N025</t>
+          <t>N002</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2712,78 +2512,78 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>N013</t>
+          <t>N019</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>N020</t>
+          <t>N002</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N014</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>N001</t>
+          <t>N017</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2792,67 +2592,67 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>N020</t>
+          <t>N015</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>N028</t>
+          <t>N001</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>N005</t>
+          <t>N012</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2863,16 +2663,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2883,152 +2683,152 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>N015</t>
+          <t>N009</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>N017</t>
+          <t>N013</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>N026</t>
+          <t>N020</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>N009</t>
+          <t>N010</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>N028</t>
+          <t>N009</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>N004</t>
+          <t>N016</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N008</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -3043,12 +2843,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -3056,19 +2856,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>N025</t>
+          <t>N016</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -3083,12 +2883,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -3096,19 +2896,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>N021</t>
+          <t>N012</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -3116,19 +2916,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>N023</t>
+          <t>N014</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -3136,19 +2936,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>N009</t>
+          <t>N006</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -3156,14 +2956,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>N023</t>
+          <t>N010</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3172,18 +2972,18 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>N017</t>
+          <t>N003</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3192,18 +2992,18 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>N010</t>
+          <t>N008</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3212,38 +3012,38 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>N003</t>
+          <t>N002</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>N002</t>
+          <t>N003</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3252,18 +3052,18 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>N028</t>
+          <t>N005</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3272,18 +3072,18 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>N001</t>
+          <t>N020</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3292,18 +3092,18 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>N016</t>
+          <t>N013</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3312,38 +3112,38 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>N020</t>
+          <t>N011</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>N012</t>
+          <t>N020</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3352,18 +3152,18 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>N008</t>
+          <t>N004</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3372,58 +3172,58 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>N003</t>
+          <t>N018</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>N006</t>
+          <t>N003</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>N024</t>
+          <t>N004</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3432,18 +3232,18 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>N014</t>
+          <t>N018</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3452,103 +3252,103 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>N001</t>
+          <t>N019</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>N015</t>
+          <t>N013</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>N026</t>
+          <t>N010</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>N023</t>
+          <t>N014</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>N019</t>
+          <t>N002</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3563,12 +3363,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -3576,19 +3376,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>N005</t>
+          <t>N018</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3596,234 +3396,234 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>N025</t>
+          <t>N004</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>N013</t>
+          <t>N005</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>N019</t>
+          <t>N012</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>N007</t>
+          <t>N018</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>N009</t>
+          <t>N005</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>N022</t>
+          <t>N017</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>N003</t>
+          <t>N020</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>N002</t>
+          <t>N006</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>N006</t>
+          <t>N005</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>N024</t>
+          <t>N006</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>N013</t>
+          <t>N017</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>N016</t>
+          <t>N019</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3832,18 +3632,18 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>N021</t>
+          <t>N007</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3852,58 +3652,58 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>N019</t>
+          <t>N016</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>N002</t>
+          <t>N008</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>N003</t>
+          <t>N005</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3912,18 +3712,18 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>N013</t>
+          <t>N019</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3932,18 +3732,18 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>N026</t>
+          <t>N012</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3952,18 +3752,18 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>N009</t>
+          <t>N001</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3972,18 +3772,18 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>N019</t>
+          <t>N015</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3996,14 +3796,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>N026</t>
+          <t>N015</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4016,14 +3816,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>N027</t>
+          <t>N015</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4036,34 +3836,34 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>N004</t>
+          <t>N012</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>N006</t>
+          <t>N004</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4072,18 +3872,18 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>N014</t>
+          <t>N011</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4092,18 +3892,18 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>N020</t>
+          <t>N008</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4112,67 +3912,67 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>N016</t>
+          <t>N005</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>N003</t>
+          <t>N013</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>N008</t>
+          <t>N013</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4183,7 +3983,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4192,1471 +3992,71 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>N002</t>
+          <t>N003</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>N010</t>
+          <t>N011</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>N011</t>
+          <t>N018</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-03-14</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>N004</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>4</v>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>N025</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>5</v>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>N011</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>0</v>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>N027</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>1</v>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>N018</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>2</v>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>N023</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2024-02-10</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>3</v>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>N010</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>N023</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>1</v>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>N005</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>2</v>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>N016</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>3</v>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>N024</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>4</v>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>N001</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>5</v>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>N021</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>0</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>N011</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>1</v>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
           <t>N015</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>2</v>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>N020</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>3</v>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>N006</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>4</v>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>N007</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>5</v>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>N010</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>N008</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>1</v>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>N012</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>2</v>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>N012</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>2024-02-11</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>3</v>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>N006</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>0</v>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>N024</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>1</v>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>N027</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>2</v>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>N002</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>3</v>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>N011</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>4</v>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>N005</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>5</v>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>N021</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>0</v>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>N004</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>1</v>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>N002</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>2</v>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>N014</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>3</v>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>N014</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>4</v>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>N028</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>5</v>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>N015</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>0</v>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>N018</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>1</v>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>N025</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>2</v>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>N016</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>2024-02-12</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>3</v>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>N025</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>0</v>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>N017</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>1</v>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>N022</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>2</v>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>N001</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>3</v>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>N011</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>4</v>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>N017</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C199" t="n">
-        <v>5</v>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>N002</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>0</v>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>N023</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
-        <v>1</v>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>N002</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C202" t="n">
-        <v>2</v>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>N003</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C203" t="n">
-        <v>3</v>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>N021</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
-        <v>4</v>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>N009</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C205" t="n">
-        <v>5</v>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>N016</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C206" t="n">
-        <v>0</v>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>N024</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>1</v>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>N023</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>2</v>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>N001</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>2024-02-13</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
-        <v>3</v>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>N013</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
-        <v>0</v>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>N016</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
-        <v>1</v>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>N002</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>2</v>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>N005</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
-        <v>3</v>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>N026</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>4</v>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>N014</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
-        <v>5</v>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>N024</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C216" t="n">
-        <v>0</v>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>N018</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C217" t="n">
-        <v>1</v>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>N012</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C218" t="n">
-        <v>2</v>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>N012</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C219" t="n">
-        <v>3</v>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>N001</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C220" t="n">
-        <v>4</v>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>N021</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="C221" t="n">
-        <v>5</v>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>N003</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C222" t="n">
-        <v>0</v>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>N009</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C223" t="n">
-        <v>1</v>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>N014</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C224" t="n">
-        <v>2</v>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>N010</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>NIGHT</t>
-        </is>
-      </c>
-      <c r="C225" t="n">
-        <v>3</v>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>N023</t>
         </is>
       </c>
     </row>
